--- a/data/Resultados_finales_tesis/Mina_modelo/Produccion_base/zona_centro/05C/P_red_gen_bat/elmo_data.xlsx
+++ b/data/Resultados_finales_tesis/Mina_modelo/Produccion_base/zona_centro/05C/P_red_gen_bat/elmo_data.xlsx
@@ -3312,7 +3312,7 @@
         <v>500</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -3339,7 +3339,7 @@
         <v>500</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3478,7 +3478,7 @@
         <v>1000</v>
       </c>
       <c r="I3" s="34" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
